--- a/output/isabel-cohorts/이사벨반_성적분석.xlsx
+++ b/output/isabel-cohorts/이사벨반_성적분석.xlsx
@@ -425,7 +425,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">3 2</t>
+          <t xml:space="preserve">3 3</t>
         </r>
         <r>
           <rPr>
@@ -441,7 +441,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">2 </t>
+          <t xml:space="preserve">3 </t>
         </r>
         <r>
           <rPr>
@@ -513,7 +513,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">1 1</t>
+          <t xml:space="preserve">1 4</t>
         </r>
         <r>
           <rPr>
@@ -741,7 +741,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B37" authorId="0">
+    <comment ref="E37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -753,7 +753,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B38" authorId="0">
+    <comment ref="E38" authorId="0">
       <text>
         <r>
           <rPr>
@@ -765,7 +765,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B39" authorId="0">
+    <comment ref="E39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -777,7 +777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B40" authorId="0">
+    <comment ref="E40" authorId="0">
       <text>
         <r>
           <rPr>
@@ -789,7 +789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C37" authorId="0">
+    <comment ref="F37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -801,7 +801,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="0">
+    <comment ref="F38" authorId="0">
       <text>
         <r>
           <rPr>
@@ -813,7 +813,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C39" authorId="0">
+    <comment ref="F39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -825,7 +825,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C40" authorId="0">
+    <comment ref="F40" authorId="0">
       <text>
         <r>
           <rPr>
@@ -837,7 +837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D37" authorId="0">
+    <comment ref="G37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -849,7 +849,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D38" authorId="0">
+    <comment ref="G38" authorId="0">
       <text>
         <r>
           <rPr>
@@ -861,7 +861,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D39" authorId="0">
+    <comment ref="G39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -873,7 +873,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D40" authorId="0">
+    <comment ref="G40" authorId="0">
       <text>
         <r>
           <rPr>
@@ -890,7 +890,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="89">
   <si>
     <r>
       <rPr>
@@ -1352,24 +1352,24 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">차 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2023–2025), </t>
+      <t xml:space="preserve">3 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 (2023–2025), </t>
     </r>
     <r>
       <rPr>
@@ -1386,7 +1386,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1·</t>
+      <t xml:space="preserve">1~</t>
     </r>
     <r>
       <rPr>
@@ -1403,7 +1403,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2 </t>
+      <t xml:space="preserve">3 </t>
     </r>
     <r>
       <rPr>
@@ -1490,7 +1490,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5</t>
+      <t xml:space="preserve">6</t>
     </r>
     <r>
       <rPr>
@@ -1524,7 +1524,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1 1</t>
+      <t xml:space="preserve">1 1~4</t>
     </r>
     <r>
       <rPr>
@@ -1576,6 +1576,23 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1·</t>
     </r>
     <r>
       <rPr>
@@ -2162,24 +2179,24 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. 2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">년 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3·4</t>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 4</t>
     </r>
     <r>
       <rPr>
@@ -2221,7 +2238,75 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">는 받은 사진에 없습니다</t>
+      <t xml:space="preserve">는 아직 기록이 없습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 구성관 총점은 성적표 두 장에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">92/93</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점으로 달라 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">92</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점을 사용했습니다</t>
     </r>
     <r>
       <rPr>
@@ -2249,75 +2334,92 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이서연반 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">년 중</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">차만 사진에 있습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. 2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">년 이시원</t>
+      <t xml:space="preserve">이서연반은 현재 중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라 고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모의고사가 없습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한재승</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">합류</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">김은혜</t>
     </r>
     <r>
       <rPr>
@@ -2334,58 +2436,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">한재승</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">합류</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">), 2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">년 김은혜</t>
+      <t xml:space="preserve">구승준</t>
     </r>
     <r>
       <rPr>
@@ -2402,23 +2453,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">구승준</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">김가민</t>
     </r>
     <r>
@@ -2428,24 +2462,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
+      <t xml:space="preserve">(2026 </t>
     </r>
     <r>
       <rPr>
@@ -4483,6 +4500,99 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">3 (2025)
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학기 중간</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 (2025)
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학기 기말</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 (2025)
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학기 중간</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">1 (2023)
 </t>
     </r>
@@ -4814,6 +4924,40 @@
   </si>
   <si>
     <t xml:space="preserve">서예준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이시원</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 (2025)
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학기 중간</t>
+    </r>
   </si>
   <si>
     <r>
@@ -5239,7 +5383,7 @@
       <rgbColor rgb="FF46AAC4"/>
       <rgbColor rgb="FF98B855"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFF59240"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF7D5FA0"/>
       <rgbColor rgb="FF9BBB59"/>
@@ -5487,7 +5631,7 @@
                   <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>86.5</c:v>
+                  <c:v>92.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5571,19 +5715,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>65.6</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>65.6</c:v>
+                  <c:v>81.3333333333333</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>80.2</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>82</c:v>
+                  <c:v>81.1666666666667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>82</c:v>
+                  <c:v>81.1666666666667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5591,11 +5735,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="75128351"/>
-        <c:axId val="87042609"/>
+        <c:axId val="7107250"/>
+        <c:axId val="49644599"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="75128351"/>
+        <c:axId val="7107250"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5627,7 +5771,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87042609"/>
+        <c:crossAx val="49644599"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5635,7 +5779,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87042609"/>
+        <c:axId val="49644599"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5679,7 +5823,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75128351"/>
+        <c:crossAx val="7107250"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6456,11 +6600,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="34642317"/>
-        <c:axId val="25906809"/>
+        <c:axId val="71357016"/>
+        <c:axId val="73525037"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="34642317"/>
+        <c:axId val="71357016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6492,7 +6636,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25906809"/>
+        <c:crossAx val="73525037"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6500,7 +6644,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25906809"/>
+        <c:axId val="73525037"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6578,7 +6722,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34642317"/>
+        <c:crossAx val="71357016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6735,9 +6879,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>구성관반_2023!$B$5:$L$5</c:f>
+              <c:f>구성관반_2023!$B$5:$M$5</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1</c:v>
@@ -6781,16 +6925,20 @@
                 <c:pt idx="10">
                   <c:v>중3 2차
 고2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>중3 3차
+고3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>구성관반_2023!$B$6:$L$6</c:f>
+              <c:f>구성관반_2023!$B$6:$M$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>71</c:v>
                 </c:pt>
@@ -6823,6 +6971,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6890,9 +7041,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>구성관반_2023!$B$5:$L$5</c:f>
+              <c:f>구성관반_2023!$B$5:$M$5</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1</c:v>
@@ -6936,16 +7087,20 @@
                 <c:pt idx="10">
                   <c:v>중3 2차
 고2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>중3 3차
+고3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>구성관반_2023!$B$7:$L$7</c:f>
+              <c:f>구성관반_2023!$B$7:$M$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>58</c:v>
                 </c:pt>
@@ -6978,6 +7133,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7045,9 +7203,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>구성관반_2023!$B$5:$L$5</c:f>
+              <c:f>구성관반_2023!$B$5:$M$5</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1</c:v>
@@ -7091,16 +7249,20 @@
                 <c:pt idx="10">
                   <c:v>중3 2차
 고2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>중3 3차
+고3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>구성관반_2023!$B$8:$L$8</c:f>
+              <c:f>구성관반_2023!$B$8:$M$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>70</c:v>
                 </c:pt>
@@ -7133,6 +7295,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>87</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7200,9 +7365,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>구성관반_2023!$B$5:$L$5</c:f>
+              <c:f>구성관반_2023!$B$5:$M$5</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1</c:v>
@@ -7246,16 +7411,20 @@
                 <c:pt idx="10">
                   <c:v>중3 2차
 고2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>중3 3차
+고3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>구성관반_2023!$B$9:$L$9</c:f>
+              <c:f>구성관반_2023!$B$9:$M$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>69</c:v>
                 </c:pt>
@@ -7288,6 +7457,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7302,11 +7474,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="85290628"/>
-        <c:axId val="94610374"/>
+        <c:axId val="75999170"/>
+        <c:axId val="58728539"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="85290628"/>
+        <c:axId val="75999170"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7338,7 +7510,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94610374"/>
+        <c:crossAx val="58728539"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7346,7 +7518,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94610374"/>
+        <c:axId val="58728539"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7424,7 +7596,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85290628"/>
+        <c:crossAx val="75999170"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7581,22 +7753,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>이서연반_2025!$B$5:$E$5</c:f>
+              <c:f>이서연반_2025!$B$5:$H$5</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>중2 3차
 고2</c:v>
                 </c:pt>
@@ -7605,20 +7789,29 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>이서연반_2025!$B$6:$E$6</c:f>
+              <c:f>이서연반_2025!$B$6:$H$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>66</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>75</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>77</c:v>
                 </c:pt>
               </c:numCache>
@@ -7687,22 +7880,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>이서연반_2025!$B$5:$E$5</c:f>
+              <c:f>이서연반_2025!$B$5:$H$5</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>중2 3차
 고2</c:v>
                 </c:pt>
@@ -7711,20 +7916,29 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>이서연반_2025!$B$7:$E$7</c:f>
+              <c:f>이서연반_2025!$B$7:$H$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>87</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>73</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>76</c:v>
                 </c:pt>
               </c:numCache>
@@ -7793,22 +8007,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>이서연반_2025!$B$5:$E$5</c:f>
+              <c:f>이서연반_2025!$B$5:$H$5</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>중2 3차
 고2</c:v>
                 </c:pt>
@@ -7817,20 +8043,29 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>이서연반_2025!$B$8:$E$8</c:f>
+              <c:f>이서연반_2025!$B$8:$H$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>88</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>87</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>100</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>95</c:v>
                 </c:pt>
               </c:numCache>
@@ -7899,22 +8134,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>이서연반_2025!$B$5:$E$5</c:f>
+              <c:f>이서연반_2025!$B$5:$H$5</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>중2 3차
 고2</c:v>
                 </c:pt>
@@ -7923,20 +8170,29 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>이서연반_2025!$B$9:$E$9</c:f>
+              <c:f>이서연반_2025!$B$9:$H$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>88</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>74</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>82</c:v>
                 </c:pt>
               </c:numCache>
@@ -8005,22 +8261,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>이서연반_2025!$B$5:$E$5</c:f>
+              <c:f>이서연반_2025!$B$5:$H$5</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>중1 1차
 고1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>중1 2차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>중1 3차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>중1 4차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>중2 1차
 고1</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>중2 2차
 고1</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>중2 3차
 고2</c:v>
                 </c:pt>
@@ -8029,21 +8297,157 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>이서연반_2025!$B$10:$E$10</c:f>
+              <c:f>이서연반_2025!$B$10:$H$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>73</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>이서연반_2025!A11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>이시원</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="f59240"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="f59240"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>이서연반_2025!$B$5:$H$5</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>중1 1차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>중1 2차
+고1</c:v>
+                </c:pt>
                 <c:pt idx="2">
-                  <c:v>82</c:v>
+                  <c:v>중1 3차
+고1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>80</c:v>
+                  <c:v>중1 4차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>중2 1차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>중2 2차
+고1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>중2 3차
+고2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>이서연반_2025!$B$11:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>77</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8058,11 +8462,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="87183825"/>
-        <c:axId val="49240210"/>
+        <c:axId val="28623653"/>
+        <c:axId val="91644827"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="87183825"/>
+        <c:axId val="28623653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8094,7 +8498,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49240210"/>
+        <c:crossAx val="91644827"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8102,7 +8506,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49240210"/>
+        <c:axId val="91644827"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8180,7 +8584,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87183825"/>
+        <c:crossAx val="28623653"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8312,8 +8716,8 @@
       <xdr:rowOff>134640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>699840</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>426960</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
@@ -8324,7 +8728,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="9048600"/>
-        <a:ext cx="6479640" cy="3239640"/>
+        <a:ext cx="6911640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8343,13 +8747,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>134640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>699840</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -8358,7 +8762,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="10001160"/>
+        <a:off x="0" y="10953720"/>
         <a:ext cx="6479640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -8707,8 +9111,8 @@
         <v>67</v>
       </c>
       <c r="D5" s="9" t="n">
-        <f aca="false">이서연반_2025!B11</f>
-        <v>65.6</v>
+        <f aca="false">이서연반_2025!B12</f>
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8724,8 +9128,8 @@
         <v>81.75</v>
       </c>
       <c r="D6" s="9" t="n">
-        <f aca="false">이서연반_2025!B11</f>
-        <v>65.6</v>
+        <f aca="false">이서연반_2025!E12</f>
+        <v>81.3333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8741,8 +9145,8 @@
         <v>94.5</v>
       </c>
       <c r="D7" s="9" t="n">
-        <f aca="false">이서연반_2025!C11</f>
-        <v>80.2</v>
+        <f aca="false">이서연반_2025!F12</f>
+        <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8758,8 +9162,8 @@
         <v>86</v>
       </c>
       <c r="D8" s="9" t="n">
-        <f aca="false">이서연반_2025!E11</f>
-        <v>82</v>
+        <f aca="false">이서연반_2025!H12</f>
+        <v>81.1666666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8771,12 +9175,12 @@
         <v>87.6666666666667</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">구성관반_2023!L10</f>
-        <v>86.5</v>
+        <f aca="false">구성관반_2023!M10</f>
+        <v>92.25</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">이서연반_2025!E11</f>
-        <v>82</v>
+        <f aca="false">이서연반_2025!H12</f>
+        <v>81.1666666666667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8793,7 +9197,7 @@
       </c>
       <c r="D10" s="11" t="n">
         <f aca="false">D8-D5</f>
-        <v>16.4</v>
+        <v>16.1666666666667</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8823,7 +9227,7 @@
         <v>14.75</v>
       </c>
       <c r="D13" s="9" t="n">
-        <f aca="false">이서연반_2025!B37</f>
+        <f aca="false">이서연반_2025!B41</f>
         <v>15</v>
       </c>
     </row>
@@ -8840,8 +9244,8 @@
         <v>20.75</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false">이서연반_2025!B37</f>
-        <v>15</v>
+        <f aca="false">이서연반_2025!E41</f>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8857,8 +9261,8 @@
         <v>25.75</v>
       </c>
       <c r="D15" s="9" t="n">
-        <f aca="false">이서연반_2025!C37</f>
-        <v>20.8</v>
+        <f aca="false">이서연반_2025!F41</f>
+        <v>20.1666666666667</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8874,8 +9278,8 @@
         <v>23.25</v>
       </c>
       <c r="D16" s="9" t="n">
-        <f aca="false">이서연반_2025!E37</f>
-        <v>21</v>
+        <f aca="false">이서연반_2025!H41</f>
+        <v>20.6666666666667</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8887,12 +9291,12 @@
         <v>23</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">구성관반_2023!L33</f>
-        <v>23</v>
+        <f aca="false">구성관반_2023!M33</f>
+        <v>24.75</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">이서연반_2025!E37</f>
-        <v>21</v>
+        <f aca="false">이서연반_2025!H41</f>
+        <v>20.6666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -10178,11 +10582,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="2" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10238,15 +10642,18 @@
         <v>43</v>
       </c>
       <c r="M5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="Q5" s="6" t="s">
         <v>49</v>
       </c>
     </row>
@@ -10287,20 +10694,23 @@
       <c r="L6" s="14" t="n">
         <v>92</v>
       </c>
-      <c r="M6" s="15" t="n">
+      <c r="M6" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="N6" s="15" t="n">
         <f aca="false">B6</f>
         <v>71</v>
       </c>
-      <c r="N6" s="15" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B6:L6)</f>
-        <v>92</v>
-      </c>
-      <c r="O6" s="16" t="n">
-        <f aca="false">N6-M6</f>
-        <v>21</v>
-      </c>
-      <c r="P6" s="15" t="n">
-        <f aca="false">MAX(B6:L6)</f>
+      <c r="O6" s="15" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B6:M6)</f>
+        <v>100</v>
+      </c>
+      <c r="P6" s="16" t="n">
+        <f aca="false">O6-N6</f>
+        <v>29</v>
+      </c>
+      <c r="Q6" s="15" t="n">
+        <f aca="false">MAX(B6:M6)</f>
         <v>100</v>
       </c>
     </row>
@@ -10341,20 +10751,23 @@
       <c r="L7" s="14" t="n">
         <v>95</v>
       </c>
-      <c r="M7" s="15" t="n">
+      <c r="M7" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="N7" s="15" t="n">
         <f aca="false">B7</f>
         <v>58</v>
       </c>
-      <c r="N7" s="15" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B7:L7)</f>
-        <v>95</v>
-      </c>
-      <c r="O7" s="16" t="n">
-        <f aca="false">N7-M7</f>
-        <v>37</v>
-      </c>
-      <c r="P7" s="15" t="n">
-        <f aca="false">MAX(B7:L7)</f>
+      <c r="O7" s="15" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B7:M7)</f>
+        <v>100</v>
+      </c>
+      <c r="P7" s="16" t="n">
+        <f aca="false">O7-N7</f>
+        <v>42</v>
+      </c>
+      <c r="Q7" s="15" t="n">
+        <f aca="false">MAX(B7:M7)</f>
         <v>100</v>
       </c>
     </row>
@@ -10395,20 +10808,23 @@
       <c r="L8" s="14" t="n">
         <v>74</v>
       </c>
-      <c r="M8" s="15" t="n">
+      <c r="M8" s="14" t="n">
+        <v>87</v>
+      </c>
+      <c r="N8" s="15" t="n">
         <f aca="false">B8</f>
         <v>70</v>
       </c>
-      <c r="N8" s="15" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B8:L8)</f>
-        <v>74</v>
-      </c>
-      <c r="O8" s="16" t="n">
-        <f aca="false">N8-M8</f>
-        <v>4</v>
-      </c>
-      <c r="P8" s="15" t="n">
-        <f aca="false">MAX(B8:L8)</f>
+      <c r="O8" s="15" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B8:M8)</f>
+        <v>87</v>
+      </c>
+      <c r="P8" s="16" t="n">
+        <f aca="false">O8-N8</f>
+        <v>17</v>
+      </c>
+      <c r="Q8" s="15" t="n">
+        <f aca="false">MAX(B8:M8)</f>
         <v>94</v>
       </c>
     </row>
@@ -10449,20 +10865,23 @@
       <c r="L9" s="14" t="n">
         <v>85</v>
       </c>
-      <c r="M9" s="15" t="n">
+      <c r="M9" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="N9" s="15" t="n">
         <f aca="false">B9</f>
         <v>69</v>
       </c>
-      <c r="N9" s="15" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B9:L9)</f>
-        <v>85</v>
-      </c>
-      <c r="O9" s="16" t="n">
-        <f aca="false">N9-M9</f>
-        <v>16</v>
-      </c>
-      <c r="P9" s="15" t="n">
-        <f aca="false">MAX(B9:L9)</f>
+      <c r="O9" s="15" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B9:M9)</f>
+        <v>82</v>
+      </c>
+      <c r="P9" s="16" t="n">
+        <f aca="false">O9-N9</f>
+        <v>13</v>
+      </c>
+      <c r="Q9" s="15" t="n">
+        <f aca="false">MAX(B9:M9)</f>
         <v>92</v>
       </c>
     </row>
@@ -10514,6 +10933,10 @@
         <f aca="false">IF(COUNT(L6:L9)=0,"",AVERAGE(L6:L9))</f>
         <v>86.5</v>
       </c>
+      <c r="M10" s="17" t="n">
+        <f aca="false">IF(COUNT(M6:M9)=0,"",AVERAGE(M6:M9))</f>
+        <v>92.25</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
@@ -10557,6 +10980,9 @@
       <c r="L13" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="M13" s="6" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
@@ -10595,6 +11021,9 @@
       <c r="L14" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="M14" s="14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
@@ -10633,6 +11062,9 @@
       <c r="L15" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="M15" s="14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
@@ -10671,6 +11103,9 @@
       <c r="L16" s="14" t="n">
         <v>3</v>
       </c>
+      <c r="M16" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
@@ -10709,6 +11144,9 @@
       <c r="L17" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="M17" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
@@ -10752,6 +11190,9 @@
       <c r="L20" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="M20" s="6" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
@@ -10790,6 +11231,9 @@
       <c r="L21" s="14" t="n">
         <v>16</v>
       </c>
+      <c r="M21" s="14" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
@@ -10828,6 +11272,9 @@
       <c r="L22" s="14" t="n">
         <v>17</v>
       </c>
+      <c r="M22" s="14" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
@@ -10866,6 +11313,9 @@
       <c r="L23" s="14" t="n">
         <v>17</v>
       </c>
+      <c r="M23" s="14" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
@@ -10904,6 +11354,9 @@
       <c r="L24" s="14" t="n">
         <v>16</v>
       </c>
+      <c r="M24" s="14" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
@@ -10953,6 +11406,10 @@
         <f aca="false">IF(COUNT(L21:L24)=0,"",AVERAGE(L21:L24))</f>
         <v>16.5</v>
       </c>
+      <c r="M25" s="17" t="n">
+        <f aca="false">IF(COUNT(M21:M24)=0,"",AVERAGE(M21:M24))</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
@@ -10996,6 +11453,9 @@
       <c r="L28" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="M28" s="6" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
@@ -11034,6 +11494,9 @@
       <c r="L29" s="14" t="n">
         <v>26</v>
       </c>
+      <c r="M29" s="14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
@@ -11072,6 +11535,9 @@
       <c r="L30" s="14" t="n">
         <v>26</v>
       </c>
+      <c r="M30" s="14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
@@ -11110,6 +11576,9 @@
       <c r="L31" s="14" t="n">
         <v>17</v>
       </c>
+      <c r="M31" s="14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
@@ -11148,6 +11617,9 @@
       <c r="L32" s="14" t="n">
         <v>23</v>
       </c>
+      <c r="M32" s="14" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
@@ -11197,6 +11669,10 @@
         <f aca="false">IF(COUNT(L29:L32)=0,"",AVERAGE(L29:L32))</f>
         <v>23</v>
       </c>
+      <c r="M33" s="17" t="n">
+        <f aca="false">IF(COUNT(M29:M32)=0,"",AVERAGE(M29:M32))</f>
+        <v>24.75</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
@@ -11217,6 +11693,15 @@
         <v>73</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>54</v>
       </c>
     </row>
@@ -11233,8 +11718,17 @@
       <c r="D37" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E37" s="18" t="n">
-        <f aca="false">IF(COUNT(B37:D37)=0,"",AVERAGE(B37:D37))</f>
+      <c r="E37" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" s="18" t="n">
+        <f aca="false">IF(COUNT(B37:G37)=0,"",AVERAGE(B37:G37))</f>
         <v>100</v>
       </c>
     </row>
@@ -11243,7 +11737,7 @@
         <v>68</v>
       </c>
       <c r="B38" s="14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C38" s="14" t="n">
         <v>100</v>
@@ -11251,9 +11745,18 @@
       <c r="D38" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E38" s="18" t="n">
-        <f aca="false">IF(COUNT(B38:D38)=0,"",AVERAGE(B38:D38))</f>
+      <c r="E38" s="14" t="n">
         <v>100</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="H38" s="18" t="n">
+        <f aca="false">IF(COUNT(B38:G38)=0,"",AVERAGE(B38:G38))</f>
+        <v>99.6666666666667</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11261,17 +11764,26 @@
         <v>69</v>
       </c>
       <c r="B39" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E39" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="C39" s="14" t="n">
+      <c r="F39" s="14" t="n">
         <v>96</v>
       </c>
-      <c r="D39" s="14" t="n">
+      <c r="G39" s="14" t="n">
         <v>98</v>
       </c>
-      <c r="E39" s="18" t="n">
-        <f aca="false">IF(COUNT(B39:D39)=0,"",AVERAGE(B39:D39))</f>
-        <v>98</v>
+      <c r="H39" s="18" t="n">
+        <f aca="false">IF(COUNT(B39:G39)=0,"",AVERAGE(B39:G39))</f>
+        <v>95.6666666666667</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11279,17 +11791,26 @@
         <v>70</v>
       </c>
       <c r="B40" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="E40" s="14" t="n">
         <v>95</v>
       </c>
-      <c r="C40" s="14" t="n">
+      <c r="F40" s="14" t="n">
         <v>98</v>
       </c>
-      <c r="D40" s="14" t="n">
+      <c r="G40" s="14" t="n">
         <v>99</v>
       </c>
-      <c r="E40" s="18" t="n">
-        <f aca="false">IF(COUNT(B40:D40)=0,"",AVERAGE(B40:D40))</f>
-        <v>97.3333333333333</v>
+      <c r="H40" s="18" t="n">
+        <f aca="false">IF(COUNT(B40:G40)=0,"",AVERAGE(B40:G40))</f>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -11310,21 +11831,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="2" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11340,519 +11861,743 @@
         <v>33</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="K5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="L5" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>63</v>
       </c>
       <c r="C6" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="F6" s="14" t="n">
         <v>66</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="G6" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="H6" s="14" t="n">
         <v>77</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="I6" s="15" t="n">
         <f aca="false">B6</f>
         <v>63</v>
       </c>
-      <c r="G6" s="15" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B6:E6)</f>
+      <c r="J6" s="15" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B6:H6)</f>
         <v>77</v>
       </c>
-      <c r="H6" s="16" t="n">
-        <f aca="false">G6-F6</f>
+      <c r="K6" s="16" t="n">
+        <f aca="false">J6-I6</f>
         <v>14</v>
       </c>
-      <c r="I6" s="15" t="n">
-        <f aca="false">MAX(B6:E6)</f>
+      <c r="L6" s="15" t="n">
+        <f aca="false">MAX(B6:H6)</f>
         <v>77</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>59</v>
       </c>
       <c r="C7" s="14" t="n">
+        <v>86</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="F7" s="14" t="n">
         <v>87</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="G7" s="14" t="n">
         <v>73</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="H7" s="14" t="n">
         <v>76</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="I7" s="15" t="n">
         <f aca="false">B7</f>
         <v>59</v>
       </c>
-      <c r="G7" s="15" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B7:E7)</f>
+      <c r="J7" s="15" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B7:H7)</f>
         <v>76</v>
       </c>
-      <c r="H7" s="16" t="n">
-        <f aca="false">G7-F7</f>
+      <c r="K7" s="16" t="n">
+        <f aca="false">J7-I7</f>
         <v>17</v>
       </c>
-      <c r="I7" s="15" t="n">
-        <f aca="false">MAX(B7:E7)</f>
+      <c r="L7" s="15" t="n">
+        <f aca="false">MAX(B7:H7)</f>
         <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>88</v>
       </c>
       <c r="C8" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="F8" s="14" t="n">
         <v>87</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="G8" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="H8" s="14" t="n">
         <v>95</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="I8" s="15" t="n">
         <f aca="false">B8</f>
         <v>88</v>
       </c>
-      <c r="G8" s="15" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B8:E8)</f>
+      <c r="J8" s="15" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B8:H8)</f>
         <v>95</v>
       </c>
-      <c r="H8" s="16" t="n">
-        <f aca="false">G8-F8</f>
+      <c r="K8" s="16" t="n">
+        <f aca="false">J8-I8</f>
         <v>7</v>
       </c>
-      <c r="I8" s="15" t="n">
-        <f aca="false">MAX(B8:E8)</f>
+      <c r="L8" s="15" t="n">
+        <f aca="false">MAX(B8:H8)</f>
         <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>67</v>
       </c>
       <c r="C9" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>71</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="F9" s="14" t="n">
         <v>88</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="G9" s="14" t="n">
         <v>74</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="H9" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="I9" s="15" t="n">
         <f aca="false">B9</f>
         <v>67</v>
       </c>
-      <c r="G9" s="15" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B9:E9)</f>
+      <c r="J9" s="15" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B9:H9)</f>
         <v>82</v>
       </c>
-      <c r="H9" s="16" t="n">
-        <f aca="false">G9-F9</f>
+      <c r="K9" s="16" t="n">
+        <f aca="false">J9-I9</f>
         <v>15</v>
       </c>
-      <c r="I9" s="15" t="n">
-        <f aca="false">MAX(B9:E9)</f>
-        <v>88</v>
+      <c r="L9" s="15" t="n">
+        <f aca="false">MAX(B9:H9)</f>
+        <v>91</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>51</v>
       </c>
       <c r="C10" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>86</v>
+      </c>
+      <c r="F10" s="14" t="n">
         <v>73</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="G10" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="H10" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="I10" s="15" t="n">
         <f aca="false">B10</f>
         <v>51</v>
       </c>
-      <c r="G10" s="15" t="n">
-        <f aca="false">LOOKUP(9.99E+307,B10:E10)</f>
+      <c r="J10" s="15" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B10:H10)</f>
         <v>80</v>
       </c>
-      <c r="H10" s="16" t="n">
-        <f aca="false">G10-F10</f>
+      <c r="K10" s="16" t="n">
+        <f aca="false">J10-I10</f>
         <v>29</v>
       </c>
-      <c r="I10" s="15" t="n">
-        <f aca="false">MAX(B10:E10)</f>
-        <v>82</v>
+      <c r="L10" s="15" t="n">
+        <f aca="false">MAX(B10:H10)</f>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>73</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>71</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <f aca="false">B11</f>
+        <v>62</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <f aca="false">LOOKUP(9.99E+307,B11:H11)</f>
+        <v>77</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <f aca="false">J11-I11</f>
+        <v>15</v>
+      </c>
+      <c r="L11" s="15" t="n">
+        <f aca="false">MAX(B11:H11)</f>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="17" t="n">
-        <f aca="false">IF(COUNT(B6:B10)=0,"",AVERAGE(B6:B10))</f>
-        <v>65.6</v>
-      </c>
-      <c r="C11" s="17" t="n">
-        <f aca="false">IF(COUNT(C6:C10)=0,"",AVERAGE(C6:C10))</f>
-        <v>80.2</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <f aca="false">IF(COUNT(D6:D10)=0,"",AVERAGE(D6:D10))</f>
-        <v>80.8</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <f aca="false">IF(COUNT(E6:E10)=0,"",AVERAGE(E6:E10))</f>
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="B12" s="17" t="n">
+        <f aca="false">IF(COUNT(B6:B11)=0,"",AVERAGE(B6:B11))</f>
+        <v>65</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <f aca="false">IF(COUNT(C6:C11)=0,"",AVERAGE(C6:C11))</f>
+        <v>73.1666666666667</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <f aca="false">IF(COUNT(D6:D11)=0,"",AVERAGE(D6:D11))</f>
+        <v>73.8333333333333</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <f aca="false">IF(COUNT(E6:E11)=0,"",AVERAGE(E6:E11))</f>
+        <v>81.3333333333333</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <f aca="false">IF(COUNT(F6:F11)=0,"",AVERAGE(F6:F11))</f>
+        <v>79</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <f aca="false">IF(COUNT(G6:G11)=0,"",AVERAGE(G6:G11))</f>
+        <v>79.1666666666667</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <f aca="false">IF(COUNT(H6:H11)=0,"",AVERAGE(H6:H11))</f>
+        <v>81.1666666666667</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="G15" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="H15" s="6" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B16" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="H16" s="14" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B17" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B18" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>2</v>
+      <c r="G18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B19" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" s="14" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="G19" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="14" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="G24" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B25" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>17</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C25" s="14"/>
       <c r="D25" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E25" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" s="14" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="E26" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="F26" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="D26" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="E26" s="14" t="n">
+      <c r="G26" s="14" t="n">
         <v>17</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B27" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="C27" s="14" t="n">
         <v>17</v>
       </c>
+      <c r="C27" s="14"/>
       <c r="D27" s="14" t="n">
         <v>17</v>
       </c>
       <c r="E27" s="14" t="n">
         <v>17</v>
       </c>
+      <c r="F27" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="17" t="n">
-        <f aca="false">IF(COUNT(B23:B27)=0,"",AVERAGE(B23:B27))</f>
+      <c r="B31" s="17" t="n">
+        <f aca="false">IF(COUNT(B25:B30)=0,"",AVERAGE(B25:B30))</f>
         <v>15.8</v>
       </c>
-      <c r="C28" s="17" t="n">
-        <f aca="false">IF(COUNT(C23:C27)=0,"",AVERAGE(C23:C27))</f>
-        <v>16.6</v>
-      </c>
-      <c r="D28" s="17" t="n">
-        <f aca="false">IF(COUNT(D23:D27)=0,"",AVERAGE(D23:D27))</f>
-        <v>16.4</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <f aca="false">IF(COUNT(E23:E27)=0,"",AVERAGE(E23:E27))</f>
-        <v>16.8</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
+      <c r="C31" s="17" t="str">
+        <f aca="false">IF(COUNT(C25:C30)=0,"",AVERAGE(C25:C30))</f>
+        <v/>
+      </c>
+      <c r="D31" s="17" t="n">
+        <f aca="false">IF(COUNT(D25:D30)=0,"",AVERAGE(D25:D30))</f>
+        <v>16.1666666666667</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <f aca="false">IF(COUNT(E25:E30)=0,"",AVERAGE(E25:E30))</f>
+        <v>16.3333333333333</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <f aca="false">IF(COUNT(F25:F30)=0,"",AVERAGE(F25:F30))</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="G31" s="17" t="n">
+        <f aca="false">IF(COUNT(G25:G30)=0,"",AVERAGE(G25:G30))</f>
+        <v>16.3333333333333</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <f aca="false">IF(COUNT(H25:H30)=0,"",AVERAGE(H25:H30))</f>
+        <v>16.8333333333333</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+    <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C34" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="G34" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>28</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11860,16 +12605,23 @@
         <v>79</v>
       </c>
       <c r="B35" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>24</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C35" s="14"/>
       <c r="D35" s="14" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11877,149 +12629,301 @@
         <v>80</v>
       </c>
       <c r="B36" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="C36" s="14" t="n">
+      <c r="C39" s="14"/>
+      <c r="D39" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="F39" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="D36" s="14" t="n">
+      <c r="G39" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="E36" s="14" t="n">
+      <c r="H39" s="14" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="17" t="n">
-        <f aca="false">IF(COUNT(B32:B36)=0,"",AVERAGE(B32:B36))</f>
+      <c r="B41" s="17" t="n">
+        <f aca="false">IF(COUNT(B35:B40)=0,"",AVERAGE(B35:B40))</f>
         <v>15</v>
       </c>
-      <c r="C37" s="17" t="n">
-        <f aca="false">IF(COUNT(C32:C36)=0,"",AVERAGE(C32:C36))</f>
-        <v>20.8</v>
-      </c>
-      <c r="D37" s="17" t="n">
-        <f aca="false">IF(COUNT(D32:D36)=0,"",AVERAGE(D32:D36))</f>
-        <v>20.8</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <f aca="false">IF(COUNT(E32:E36)=0,"",AVERAGE(E32:E36))</f>
+      <c r="C41" s="17" t="str">
+        <f aca="false">IF(COUNT(C35:C40)=0,"",AVERAGE(C35:C40))</f>
+        <v/>
+      </c>
+      <c r="D41" s="17" t="n">
+        <f aca="false">IF(COUNT(D35:D40)=0,"",AVERAGE(D35:D40))</f>
+        <v>18</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <f aca="false">IF(COUNT(E35:E40)=0,"",AVERAGE(E35:E40))</f>
         <v>21</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
+      <c r="F41" s="17" t="n">
+        <f aca="false">IF(COUNT(F35:F40)=0,"",AVERAGE(F35:F40))</f>
+        <v>20.1666666666667</v>
+      </c>
+      <c r="G41" s="17" t="n">
+        <f aca="false">IF(COUNT(G35:G40)=0,"",AVERAGE(G35:G40))</f>
+        <v>20.3333333333333</v>
+      </c>
+      <c r="H41" s="17" t="n">
+        <f aca="false">IF(COUNT(H35:H40)=0,"",AVERAGE(H35:H40))</f>
+        <v>20.6666666666667</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+    <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E40" s="6" t="s">
+      <c r="B44" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" s="6" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>97</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <f aca="false">IF(COUNT(B41:D41)=0,"",AVERAGE(B41:D41))</f>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B42" s="14" t="n">
-        <v>89</v>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>94</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <f aca="false">IF(COUNT(B42:D42)=0,"",AVERAGE(B42:D42))</f>
-        <v>94.3333333333333</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B43" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>99</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <f aca="false">IF(COUNT(B43:D43)=0,"",AVERAGE(B43:D43))</f>
-        <v>99.6666666666667</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="14" t="n">
-        <v>95</v>
-      </c>
-      <c r="C44" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>95</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <f aca="false">IF(COUNT(B44:D44)=0,"",AVERAGE(B44:D44))</f>
-        <v>96.6666666666667</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="14" t="n">
+        <v>97</v>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>97</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <f aca="false">IF(COUNT(B45:E45)=0,"",AVERAGE(B45:E45))</f>
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B45" s="14" t="n">
+      <c r="B46" s="14" t="n">
+        <v>98</v>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <f aca="false">IF(COUNT(B46:E46)=0,"",AVERAGE(B46:E46))</f>
+        <v>95.25</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="F47" s="18" t="n">
+        <f aca="false">IF(COUNT(B47:E47)=0,"",AVERAGE(B47:E47))</f>
+        <v>99.75</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C48" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="F48" s="18" t="n">
+        <f aca="false">IF(COUNT(B48:E48)=0,"",AVERAGE(B48:E48))</f>
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="C49" s="14" t="n">
         <v>88</v>
       </c>
-      <c r="C45" s="14" t="n">
+      <c r="D49" s="14" t="n">
         <v>85</v>
       </c>
-      <c r="D45" s="14" t="n">
+      <c r="E49" s="14" t="n">
         <v>92</v>
       </c>
-      <c r="E45" s="18" t="n">
-        <f aca="false">IF(COUNT(B45:D45)=0,"",AVERAGE(B45:D45))</f>
-        <v>88.3333333333333</v>
+      <c r="F49" s="18" t="n">
+        <f aca="false">IF(COUNT(B49:E49)=0,"",AVERAGE(B49:E49))</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <f aca="false">IF(COUNT(B50:E50)=0,"",AVERAGE(B50:E50))</f>
+        <v>96.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/isabel-cohorts/이사벨반_성적분석.xlsx
+++ b/output/isabel-cohorts/이사벨반_성적분석.xlsx
@@ -2213,32 +2213,66 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">는 아직 기록이 없습니다</t>
+      <t xml:space="preserve">(2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학년도 수능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불수능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이라 제외했습니다</t>
     </r>
     <r>
       <rPr>
@@ -5735,11 +5769,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="7107250"/>
-        <c:axId val="49644599"/>
+        <c:axId val="52494468"/>
+        <c:axId val="47625029"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="7107250"/>
+        <c:axId val="52494468"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5771,7 +5805,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49644599"/>
+        <c:crossAx val="47625029"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5779,7 +5813,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49644599"/>
+        <c:axId val="47625029"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5823,7 +5857,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7107250"/>
+        <c:crossAx val="52494468"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6600,11 +6634,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="71357016"/>
-        <c:axId val="73525037"/>
+        <c:axId val="49976651"/>
+        <c:axId val="82987716"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="71357016"/>
+        <c:axId val="49976651"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6636,7 +6670,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73525037"/>
+        <c:crossAx val="82987716"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6644,7 +6678,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73525037"/>
+        <c:axId val="82987716"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6722,7 +6756,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71357016"/>
+        <c:crossAx val="49976651"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7474,11 +7508,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="75999170"/>
-        <c:axId val="58728539"/>
+        <c:axId val="30787940"/>
+        <c:axId val="56939520"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="75999170"/>
+        <c:axId val="30787940"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7510,7 +7544,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58728539"/>
+        <c:crossAx val="56939520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7518,7 +7552,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58728539"/>
+        <c:axId val="56939520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7596,7 +7630,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75999170"/>
+        <c:crossAx val="30787940"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8462,11 +8496,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="28623653"/>
-        <c:axId val="91644827"/>
+        <c:axId val="90338665"/>
+        <c:axId val="83676905"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="28623653"/>
+        <c:axId val="90338665"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8498,7 +8532,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91644827"/>
+        <c:crossAx val="83676905"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8506,7 +8540,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91644827"/>
+        <c:axId val="83676905"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8584,7 +8618,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28623653"/>
+        <c:crossAx val="90338665"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/output/isabel-cohorts/이사벨반_성적분석.xlsx
+++ b/output/isabel-cohorts/이사벨반_성적분석.xlsx
@@ -2281,74 +2281,6 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">중</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">차 구성관 총점은 성적표 두 장에 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">92/93</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점으로 달라 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">92</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점을 사용했습니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">.</t>
     </r>
   </si>
@@ -5769,11 +5701,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="52494468"/>
-        <c:axId val="47625029"/>
+        <c:axId val="88649316"/>
+        <c:axId val="90982031"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="52494468"/>
+        <c:axId val="88649316"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5805,7 +5737,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47625029"/>
+        <c:crossAx val="90982031"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5813,7 +5745,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="47625029"/>
+        <c:axId val="90982031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5857,7 +5789,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52494468"/>
+        <c:crossAx val="88649316"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6634,11 +6566,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="49976651"/>
-        <c:axId val="82987716"/>
+        <c:axId val="79998907"/>
+        <c:axId val="65371069"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="49976651"/>
+        <c:axId val="79998907"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6670,7 +6602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82987716"/>
+        <c:crossAx val="65371069"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6678,7 +6610,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82987716"/>
+        <c:axId val="65371069"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6756,7 +6688,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49976651"/>
+        <c:crossAx val="79998907"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7004,7 +6936,7 @@
                   <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>92</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>100</c:v>
@@ -7508,11 +7440,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="30787940"/>
-        <c:axId val="56939520"/>
+        <c:axId val="82631256"/>
+        <c:axId val="45236961"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="30787940"/>
+        <c:axId val="82631256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7544,7 +7476,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56939520"/>
+        <c:crossAx val="45236961"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7552,7 +7484,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56939520"/>
+        <c:axId val="45236961"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7630,7 +7562,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30787940"/>
+        <c:crossAx val="82631256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8496,11 +8428,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="90338665"/>
-        <c:axId val="83676905"/>
+        <c:axId val="81600525"/>
+        <c:axId val="17530838"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="90338665"/>
+        <c:axId val="81600525"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8532,7 +8464,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83676905"/>
+        <c:crossAx val="17530838"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8540,7 +8472,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83676905"/>
+        <c:axId val="17530838"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8618,7 +8550,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90338665"/>
+        <c:crossAx val="81600525"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10726,7 +10658,7 @@
         <v>95</v>
       </c>
       <c r="L6" s="14" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M6" s="14" t="n">
         <v>100</v>
@@ -10965,7 +10897,7 @@
       </c>
       <c r="L10" s="17" t="n">
         <f aca="false">IF(COUNT(L6:L9)=0,"",AVERAGE(L6:L9))</f>
-        <v>86.5</v>
+        <v>86.75</v>
       </c>
       <c r="M10" s="17" t="n">
         <f aca="false">IF(COUNT(M6:M9)=0,"",AVERAGE(M6:M9))</f>
